--- a/I-O Files/shopify_products.xlsx
+++ b/I-O Files/shopify_products.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/161581077d7d95ba/Documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{BA4B2EB0-0030-4A7D-8424-F921B8B67E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942184AD-D236-48EB-8F42-0586E88E2790}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Title</t>
   </si>
@@ -31,47 +25,125 @@
     <t>Inventory Quantity</t>
   </si>
   <si>
+    <t>amazon ac</t>
+  </si>
+  <si>
+    <t>canon29</t>
+  </si>
+  <si>
+    <t>diary</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
+    <t>infinix inbook</t>
+  </si>
+  <si>
+    <t>monitor</t>
+  </si>
+  <si>
     <t>Mouse</t>
   </si>
   <si>
+    <t>Mouse1</t>
+  </si>
+  <si>
     <t>Pen</t>
   </si>
   <si>
+    <t>Pen1</t>
+  </si>
+  <si>
+    <t>realme-1</t>
+  </si>
+  <si>
     <t>Shirt</t>
   </si>
   <si>
+    <t>Shirt1</t>
+  </si>
+  <si>
     <t>T-shirt</t>
   </si>
   <si>
+    <t>T-shirt1</t>
+  </si>
+  <si>
     <t>Trousers</t>
   </si>
   <si>
+    <t>Trousers1</t>
+  </si>
+  <si>
     <t>water bottle</t>
   </si>
   <si>
+    <t>water bottle1</t>
+  </si>
+  <si>
+    <t>SKU019</t>
+  </si>
+  <si>
+    <t>SKU009</t>
+  </si>
+  <si>
+    <t>SKU010</t>
+  </si>
+  <si>
+    <t>SKU012</t>
+  </si>
+  <si>
+    <t>SKU008</t>
+  </si>
+  <si>
+    <t>SKU011</t>
+  </si>
+  <si>
     <t>SKU001</t>
   </si>
   <si>
+    <t>SKU013</t>
+  </si>
+  <si>
     <t>SKU002</t>
   </si>
   <si>
+    <t>SKU014</t>
+  </si>
+  <si>
+    <t>SKU007</t>
+  </si>
+  <si>
     <t>SKU003</t>
   </si>
   <si>
+    <t>SKU015</t>
+  </si>
+  <si>
     <t>SKU004</t>
   </si>
   <si>
+    <t>SKU016</t>
+  </si>
+  <si>
     <t>SKU005</t>
   </si>
   <si>
+    <t>SKU017</t>
+  </si>
+  <si>
     <t>SKU006</t>
+  </si>
+  <si>
+    <t>SKU018</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,12 +155,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -140,25 +206,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +250,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +284,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +318,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,14 +493,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,74 +508,216 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>100</v>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>